--- a/outputs/daily/hr_rankings_2026-07-11_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-11_full.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2226,34 +2222,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8587,56 +8579,56 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>804668</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Rafael Flores Jr.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8650,26 +8642,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>51.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.2</v>
+        <v>32.8</v>
       </c>
       <c r="R30" t="n">
-        <v>68.09999999999999</v>
+        <v>47.8</v>
       </c>
       <c r="S30" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>73.2</v>
+        <v>63.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8683,7 +8675,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8704,7 +8696,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8716,32 +8708,32 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/7 over last 3 games</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8751,112 +8743,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>91.58</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>102.6264</t>
+          <t>102.6343</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4734</t>
+          <t>0.7821</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3377</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.4396</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8867,52 +8859,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>804668</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rafael Flores Jr.</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -8930,26 +8922,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>72.59999999999999</v>
+        <v>51.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>32.8</v>
+        <v>51.2</v>
       </c>
       <c r="R31" t="n">
-        <v>47.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T31" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>63.3</v>
+        <v>70.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8963,7 +8955,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8984,7 +8976,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8996,32 +8988,32 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Contact streak: 3/7 over last 3 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9031,112 +9023,112 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>91.58</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.6343</t>
+          <t>102.6264</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.7821</t>
+          <t>0.4734</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>0.3377</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.4396</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -11482,34 +11474,30 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12050,34 +12038,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16248,28 +16232,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19515,22 +19503,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19545,22 +19533,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -19578,26 +19566,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>33.6</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="n">
-        <v>51.2</v>
+        <v>31.6</v>
       </c>
       <c r="R69" t="n">
-        <v>68.09999999999999</v>
+        <v>40.1</v>
       </c>
       <c r="S69" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U69" t="n">
-        <v>52.3</v>
+        <v>7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19611,7 +19599,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19632,7 +19620,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19649,27 +19637,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19679,112 +19667,112 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>100.1077</t>
+          <t>102.7141</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.5116</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.2285</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.2416</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19795,47 +19783,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19858,61 +19846,65 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>57</v>
+        <v>49.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>31.6</v>
+        <v>42.9</v>
       </c>
       <c r="R70" t="n">
-        <v>40.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S70" t="n">
-        <v>93.2</v>
+        <v>59.8</v>
       </c>
       <c r="T70" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19929,27 +19921,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19959,112 +19951,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>102.7141</t>
+          <t>102.5598</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.5116</t>
+          <t>0.4464</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2285</t>
+          <t>0.2043</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.2416</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20075,56 +20067,56 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20138,65 +20130,61 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>49.6</v>
+        <v>33.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>42.9</v>
+        <v>51.2</v>
       </c>
       <c r="R71" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T71" t="n">
         <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>62</v>
+        <v>50.3</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20213,27 +20201,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20243,97 +20231,97 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>102.5598</t>
+          <t>100.1077</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.4464</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.2043</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
@@ -20343,12 +20331,12 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -22978,34 +22966,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30554,34 +30538,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35763,47 +35743,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>656484</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tristan Gray</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35830,22 +35810,22 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>43.8</v>
+        <v>34.9</v>
       </c>
       <c r="R127" t="n">
-        <v>68.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="S127" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T127" t="n">
         <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>4.5</v>
+        <v>59.1</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35859,7 +35839,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35897,132 +35877,132 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>100.6168</t>
+          <t>98.614</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.4224</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.1703</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
@@ -36032,7 +36012,7 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36043,32 +36023,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36078,12 +36058,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -36110,13 +36090,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>29.3</v>
+        <v>24.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>34.9</v>
+        <v>49.5</v>
       </c>
       <c r="R128" t="n">
-        <v>40.2</v>
+        <v>41.1</v>
       </c>
       <c r="S128" t="n">
         <v>86.40000000000001</v>
@@ -36125,7 +36105,7 @@
         <v>80</v>
       </c>
       <c r="U128" t="n">
-        <v>59.1</v>
+        <v>15.3</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -36177,27 +36157,27 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -36207,112 +36187,112 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>38.68</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>98.614</t>
+          <t>99.2618</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4224</t>
+          <t>0.4073</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1373</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -36323,47 +36303,47 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>656484</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Tristan Gray</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36372,7 +36352,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36390,22 +36370,22 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>24.8</v>
+        <v>32.7</v>
       </c>
       <c r="Q129" t="n">
-        <v>49.5</v>
+        <v>43.8</v>
       </c>
       <c r="R129" t="n">
-        <v>41.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S129" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T129" t="n">
         <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>15.3</v>
+        <v>3.4</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36419,7 +36399,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36457,12 +36437,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -36472,127 +36452,127 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>99.2618</t>
+          <t>100.6168</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.4073</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1373</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -39766,34 +39746,30 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41166,34 +41142,30 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41730,34 +41702,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44522,34 +44490,30 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45086,34 +45050,30 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46490,34 +46450,30 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -50962,34 +50918,30 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52918,34 +52870,30 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -54362,7 +54310,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -54372,7 +54320,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/14, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
@@ -62392,7 +62340,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -62425,7 +62373,7 @@
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>42</v>
+        <v>39.8</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -62482,7 +62430,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -62492,7 +62440,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -64670,34 +64618,30 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB230" t="inlineStr"/>
       <c r="AC230" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -69339,56 +69283,56 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -69402,61 +69346,57 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P247" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="Q247" t="n">
-        <v>49.5</v>
+        <v>31.6</v>
       </c>
       <c r="R247" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S247" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T247" t="n">
         <v>50</v>
       </c>
       <c r="U247" t="n">
-        <v>5.7</v>
+        <v>81.7</v>
       </c>
       <c r="V247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W247" t="inlineStr">
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr"/>
@@ -69473,27 +69413,27 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -69503,112 +69443,112 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>94.7182</t>
+          <t>97.9126</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>0.3109</t>
+          <t>0.3243</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>0.0939</t>
+          <t>0.0973</t>
         </is>
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.2614</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>0.0409</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE247" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH247" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr"/>
@@ -69619,22 +69559,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>645302</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -69644,22 +69584,22 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -69668,7 +69608,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -69686,22 +69626,22 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>10.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q248" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="R248" t="n">
-        <v>35</v>
+        <v>41.1</v>
       </c>
       <c r="S248" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T248" t="n">
         <v>50</v>
       </c>
       <c r="U248" t="n">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -69715,7 +69655,7 @@
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -69753,12 +69693,12 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -69768,12 +69708,12 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
@@ -69783,87 +69723,87 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>97.6261</t>
+          <t>94.7182</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3109</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>0.0739</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>0.2799</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.0409</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD248" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE248" t="inlineStr">
@@ -69873,7 +69813,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr">
@@ -69888,7 +69828,7 @@
       </c>
       <c r="BI248" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ248" t="inlineStr"/>
@@ -69899,47 +69839,47 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -69948,7 +69888,7 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -69962,26 +69902,26 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q249" t="n">
-        <v>35.1</v>
+        <v>50.2</v>
       </c>
       <c r="R249" t="n">
-        <v>41.1</v>
+        <v>35</v>
       </c>
       <c r="S249" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T249" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U249" t="n">
-        <v>38.3</v>
+        <v>10.6</v>
       </c>
       <c r="V249" t="inlineStr">
         <is>
@@ -69995,7 +69935,7 @@
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -70016,7 +69956,7 @@
       <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr"/>
@@ -70033,12 +69973,12 @@
       </c>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
@@ -70048,112 +69988,112 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Contact streak: 6/16 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>95.4416</t>
+          <t>97.6261</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>0.2683</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>0.0412</t>
+          <t>0.0739</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>0.2561</t>
+          <t>0.2799</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="BE249" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>27.34</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr">
@@ -70168,7 +70108,7 @@
       </c>
       <c r="BI249" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ249" t="inlineStr"/>
@@ -70179,32 +70119,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>682729</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -70214,12 +70154,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -70242,65 +70182,61 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q250" t="n">
-        <v>44.5</v>
+        <v>35.1</v>
       </c>
       <c r="R250" t="n">
-        <v>22.6</v>
+        <v>41.1</v>
       </c>
       <c r="S250" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T250" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U250" t="n">
-        <v>41.2</v>
+        <v>38.3</v>
       </c>
       <c r="V250" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr"/>
@@ -70312,139 +70248,147 @@
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>Last 4 games: 3/11, 1 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>93.3128</t>
+          <t>95.4416</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>0.2528</t>
+          <t>0.2683</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.0412</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>0.1909</t>
+          <t>0.2561</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>66.86</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>35.41</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD250" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE250" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="BG250" t="inlineStr"/>
-      <c r="BH250" t="inlineStr"/>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI250" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ250" t="inlineStr"/>
@@ -70455,47 +70399,47 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>683083</t>
+          <t>682729</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Nasim Nuñez</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -70504,7 +70448,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -70518,58 +70462,62 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="Q251" t="n">
-        <v>33.9</v>
+        <v>44.5</v>
       </c>
       <c r="R251" t="n">
-        <v>40.2</v>
+        <v>22.6</v>
       </c>
       <c r="S251" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T251" t="n">
         <v>75</v>
       </c>
       <c r="U251" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W251" t="inlineStr">
+      <c r="Z251" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70584,17 +70532,17 @@
       </c>
       <c r="AG251" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ251" t="inlineStr">
@@ -70604,127 +70552,119 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 4 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>86.01</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>96.0075</t>
+          <t>93.3128</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>0.2984</t>
+          <t>0.2528</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD251" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE251" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>26.81</t>
-        </is>
-      </c>
-      <c r="BG251" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH251" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
       <c r="BI251" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ251" t="inlineStr"/>
@@ -70735,47 +70675,47 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>683083</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Nasim Nuñez</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -70798,62 +70738,58 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P252" t="n">
-        <v>14.3</v>
+        <v>5</v>
       </c>
       <c r="Q252" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="R252" t="n">
-        <v>22.1</v>
+        <v>40.2</v>
       </c>
       <c r="S252" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T252" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>10.6</v>
+        <v>54.9</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr"/>
       <c r="AC252" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70873,27 +70809,27 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -70903,72 +70839,72 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>86.01</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>98.5487</t>
+          <t>96.0075</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.2984</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
+          <t>0.0741</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>0.2771</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>68.77</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>32.83</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>18.68</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="AT252" t="inlineStr">
-        <is>
-          <t>0.2951</t>
-        </is>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
-      </c>
-      <c r="AV252" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AW252" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
-      </c>
-      <c r="AX252" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AY252" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AZ252" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
@@ -70978,29 +70914,37 @@
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>27.23</t>
-        </is>
-      </c>
-      <c r="BG252" t="inlineStr"/>
-      <c r="BH252" t="inlineStr"/>
+          <t>26.81</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -71011,56 +70955,56 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L253" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -71074,61 +71018,65 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q253" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="R253" t="n">
-        <v>40.1</v>
+        <v>22.1</v>
       </c>
       <c r="S253" t="n">
-        <v>44.8</v>
+        <v>71.7</v>
       </c>
       <c r="T253" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W253" t="inlineStr">
+      <c r="Z253" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr"/>
@@ -71145,12 +71093,12 @@
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -71160,127 +71108,119 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>96.0986</t>
+          <t>98.5487</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0875</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.1813</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD253" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE253" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="BG253" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH253" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>27.23</t>
+        </is>
+      </c>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ253" t="inlineStr"/>
@@ -71662,34 +71602,30 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB255" t="inlineStr"/>
       <c r="AC255" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -71944,28 +71880,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W256" t="inlineStr"/>
-      <c r="X256" t="inlineStr"/>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y256" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB256" t="inlineStr"/>
       <c r="AC256" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74216,34 +74156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75616,34 +75552,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
